--- a/CUI_cartera_GN_consolidado.xlsx
+++ b/CUI_cartera_GN_consolidado.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Solo_Nuevos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Todas_las_Fuentes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BI_no_en_Carteras" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21161,4 +21166,7643 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CUI</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NOMBRE_INVERSION</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SECTOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ENTIDAD</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>NOM_UEP</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SITUACION</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO_INVERSION</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DES_TIPOLOGIA</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>COSTO_ACTUALIZADO</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FECHA_REGISTRO</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>FECHA_VIABILIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2001324</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SUSTITUCION DE LA INFRAESTRUCTURA PROVISIONAL DEL C.N N° 5130 (EX-ANEXO MANUEL SEOANE CORRALES)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALU</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>6162389</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PROVINCIA CONSTITUCIONAL DEL CALLAO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>VENTANILLA</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>37109</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>38189</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2022074</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE LA INFRAESTRUCTURA Y DOTACION DE MOBILIARIO ESCOLAR DEL CEM SAN ANTONIO DE PADUA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALU</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1078192</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>VICTOR FAJARDO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>COLCA</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>38372</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>38422</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2001318</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SUSTITUCION DE LAS AULAS PREFABRICADAS CON LA CONSTRUCCION DEL LOCAL ESCOLAR PARA EL CENTRO EDUCATIVO 10 DE MARZO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>995693</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>37456</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>37953</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2002120</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SUSTITUCION DE INFRAESTRUCTURA DEL C.E N° 32384 SARA VIZURRAGA DOMINGUEZ (EX-CESAR OCTAVIO VERGARA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>817394</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>HUAMALIES</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>LLATA</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>37442</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>37594</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2002125</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SUSTITUCION, REHABILITACION Y ADECUACION DE INFRAESTRUCTURA EN EL COMPLEJO EDUCATIVO SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1091943</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AYABACA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AYABACA</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>37589</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>37992</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017353</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SUSTITUCION DE LA INFRAESTRUCTURA Y EQUIPAMIENTO DEL COLEGIO NACIONAL MICAELA BASTIDAS PUYUCCAHUA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1196241</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CANAS</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PAMPAMARCA</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>38134</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>38195</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017614</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SUSTITUCION DE INFRAESTRUCTURA DEL CENTRO EDUCATIVO GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1175989.51</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>VICTOR FAJARDO</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CANARIA</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>37809</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>37970</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2030355</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SUSTITUCIÓN DE LA INFRAESTRUCTURA Y EQUIPAMIENTO DE LA INSTITUCION EDUCATIVA N° 86278 MARIO TORRES MEZARINA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1908216</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CARHUAZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ANTA</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>38755</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>38985</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2439597</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0020 EN LA LOCALIDAD SAN MARTIN DE PORRES, DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>590779.41</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2439601</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0092, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>789599.8100000001</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2439604</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0115 11 - DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>223846.69</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2439607</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 2040 REPUBLICA DE CUBA, DISTRITO DE COMAS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1896814.45</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2439609</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0091 SANTA FE, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>171211.23</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2439611</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 1236, DISTRITO DE ATE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>105322.24</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2439616</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE SAN MARTIN DE PORRES, DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN BÁSICA ESPECIAL - CEBE</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>491292.17</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2439633</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0150 HEROES DE LA BREÑA - DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>325647.8</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2465954</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE EQUIPO DE AULA DE INNOVACION PEDAGOGICA; EN II.EE. PRIMARIA, II.EE. SECUNDARIA A NIVEL NACIONAL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1441458.83</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CHEPEN</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>CHEPEN</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>43753</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>43756</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2475388</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RENOVACION DE CERCO PERIMÉTRICO; EN EL(LA) INSTITUTO SUPERIOR TECNOLÓGICO JULIO CESAR TELLO EN LA LOCALIDAD VILLA EL SALVADOR, DISTRITO DE VILLA EL SALVADOR, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SUPERIOR TECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3961732.92</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>43829</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>43829</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2488969</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA DE EDUCACION PRIMARIA; EN EL(LA) IE 2078 NUESTRA SEÑORA DE LOURDES - LOS OLIVOS SANTA LUISA DISTRITO DE LOS OLIVOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1151292.9</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>43987</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>43987</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2494336</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE EQUIPAMIENTO DE AULA DE INNOVACION PEDAGOGICA; EN SIETE II.EE. PRIMARIA, II.EE. SECUNDARIA A NIVEL PROVINCIAL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>523812.78</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>44047</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>44057</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2495510</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE EQUIPO DE AULA DE INNOVACION PEDAGOGICA; EN CIENTO VEINTICUATRO II.EE. PRIMARIA, II.EE. SECUNDARIA A NIVEL PROVINCIAL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>8884139.189999999</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>44061</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>44061</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2495534</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE MOBILIARIO DE AULA DE EDUCACION INICIAL Y MOBILIARIO DE AULA DE EDUCACION PRIMARIA; EN CINCO II.EE. INICIAL, II.EE. PRIMARIA A NIVEL PROVINCIAL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>182544</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>44061</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>44061</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2508718</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA DE EDUCACION PRIMARIA; EN EL(LA) IE 7220 - VILLA MARIA DEL TRIUNFO  DISTRITO DE VILLA MARIA DEL TRIUNFO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>852626.4399999999</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>VILLA MARIA DEL TRIUNFO</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>44194</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>44194</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2560356</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE MOBILIARIO DE AULA DE EDUCACION INICIAL, MOBILIARIO DE AULA DE EDUCACION PRIMARIA, MOBILIARIO DE AULA DE EDUCACION SECUNDARIA Y MOBILIARIO DE SALA PSICOMOTRICIDAD; ADEMÁS DE OTROS ACTIVOS EN CIENTO CINCUENTA Y CINCO II.EE. INICIAL, II.EE. PRIMARIA, II.EE. SECUNDARIA A NIVEL DEPARTAMENTAL (LIMA)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>32227176.04</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>44881</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2664559</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE EQUIPOS COMPLEMENTARIOS, IMPRESORA MULTIFUNCIONAL, ESCANER Y EQUIPOS COMPLEMENTARIOS; ADEMÁS DE OTROS ACTIVOS EN EL(LA) PROGRAMA NACIONAL DE INFRAESTRUCTURA EDUCATIVA  DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TIC</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>5125332.2</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>45580</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>45581</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2669378</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE EQUIPO DE AULA DE INNOVACION PEDAGOGICA, EQUIPO DE OTROS ACTIVOS COMPLEMENTARIOS, MOBILIARIO DE AULA DE INNOVACION PEDAGOGICA Y MOBILIARIO DE AULA DE EDUCACION INICIAL; ADEMÁS DE OTROS ACTIVOS EN DOSCIENTOS SETENTA Y OCHO II.EE. INICIAL, II.EE. PRIMARIA, II.EE. SECUNDARIA A NIVEL DEPARTAMENTAL (LIMA)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>56907393.96</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>45617</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>45660</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2710011</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SERVIDOR, SISTEMAS DE PROCESAMIENTO Y ALMACENAMIENTO (SERVIDORES, STORAGE, LIBRERIAS DE RESPALDO, CLOUDBRIDGE), GABINETE DE COMUNICACIONES Y CENTRO DE DATOS; ADEMÁS DE OTROS ACTIVOS EN EL(LA) PRONIED  DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TIC</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>14220297.8</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>45971</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2715713</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE AULA DE EDUCACION SUPERIOR TECNOLOGICA, LABORATORIO Y LABORATORIO Y/O TALLER; ADQUISICION DE MOBILIARIO DE AULA; ADEMÁS DE OTROS ACTIVOS EN EL(LA) INSTITUTO DE EDUCACION SUPERIOR TECNOLOGICO PUBLICO MISIONEROS MONFORTIANOS EN EL CENTRO POBLADO LA VICTORIA, DISTRITO DE CHACLACAYO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SUPERIOR TECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>5222067.4</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>CHACLACAYO</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2520537</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PROYECTO ESPECIAL DE INVERSION PUBLICA ESCUELAS BICENTENARIo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PROYECTO ESPECIAL DE INVERSION PUBLICA ESCUELAS BICENTENARIO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PROYECTO PEIP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>381666124.83</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>44272</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2014811</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SUSTITUCION Y CONSTRUCCION DE INFRAESTRUCTURA DEL COLEGIO NACIONAL N° 7037 ARIOSTO MATELLINI ESPINOZA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>910682</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>37781</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>37781</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2017610</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SUSTITUCION Y AMPLIACION DE LA INFRAESTRUCTURA DEL CENTRO EDUCATIVO N° 10126 NUESTRA SEÑORA DE FATIMA-LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>1969752.19</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>JAYANCA</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>38019</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>38156</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2018252</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SUSTITUCION DE INFRAESTRUCTURA DEL C.N. N° 88389 JUAN VALER SANDOVAL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VIVIENDA, CONSTRUCCION Y SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INFRAESTRUCTURA EDUCATIVA Y DE SALUD - INFES</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>1873232</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NUEVO CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>37670</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>38027</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2088778</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION E IMPLEMENTACION DEL NUEVO LOCAL DEL MINISTERIO DE EDUCACION PARA LA MEJORA DE LOS SERVICIOS BRINDADOS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PIP MAYOR (SNIP)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>43446302</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>SAN BORJA</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>39804</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2383242</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0092 - SAN JUAN DE LURIGANCHO  DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>285122.6</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2383243</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0020 - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>104821.52</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2383249</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE GRAN MARISCAL ANDRES A.CACERES D. - EL AGUSTINO  DISTRITO DE EL AGUSTINO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>173380.29</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>43180</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>43187</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2383269</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 1148 JUANA INFANTES VERA - LIMA EN LA LOCALIDAD LIMA, DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>335494.81</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2383270</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0091 SANTA FE - SAN JUAN DE LURIGANCHO EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>163150.23</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2383271</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE LIBERTADOR SAN MARTIN - INDEPENDENCIA  DISTRITO DE INDEPENDENCIA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>288661.8</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="N40" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O40" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2383273</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0150 HEROES DE LA BREÑA - SAN JUAN DE LURIGANCHO EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>310421.8</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O41" s="1" t="n">
+        <v>43175</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2383275</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 3038 PATRICIA CARMEN GUZMAN - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>85352.28</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N42" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2383280</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 117 RVDO. PADRE PASCUAL ALEGRE GONZALES - LIMA EN LA LOCALIDAD LIMA, DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>211684.67</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2383281</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0115 11 - SAN JUAN DE LURIGANCHO EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>208620.69</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O44" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2383282</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0043 JUAN PABLO II - SAN JUAN DE LURIGANCHO  DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>160871.84</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N45" s="1" t="n">
+        <v>43174</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>43180</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2383284</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0115 08 WILLIAM DYER AMPUDIA - SAN JUAN DE LURIGANCHO EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>75322.92999999999</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2383287</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE PADRE CARLOS - SAN JUAN DE LURIGANCHO EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>116431.96</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N47" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2383289</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) 325061 - 0901892  - CETPRO SEÑOR DE LOS MILAGROS EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN TÉCNICO PRODUCTIVA</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>342899.12</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2383291</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0377 DIVINO NIÑO JESUS - LOS OLIVOS  DISTRITO DE LOS OLIVOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>81927.44</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2383292</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) 0533950 - CETPRO FRANCISCO GARCIA CALDERON EN LA LOCALIDAD PUEBLO LIBRE, DISTRITO DE PUEBLO LIBRE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN TÉCNICO PRODUCTIVA</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>53943.52</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>PUEBLO LIBRE</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O50" s="1" t="n">
+        <v>43175</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2383294</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE SAN MARTIN DE PORRES - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN BÁSICA ESPECIAL </t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>474378.17</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>43180</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>43187</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2383295</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 06 REPUBLICA DOMINICANA - LIMA  DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN BÁSICA ESPECIAL </t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>380783.57</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O52" s="1" t="n">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2383297</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE LUIS ENRIQUE XIX - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>93466.44</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>43174</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>43187</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2383299</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 555 INMACULADA CONCEPCION - SANTIAGO DE SURCO  DISTRITO DE SANTIAGO DE SURCO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>141791.6</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="n">
+        <v>43173</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2383305</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE MI MUNDO FELIZ - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>64013</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="n">
+        <v>43174</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2383310</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 7068 ABRAHAM ROLDAN POMA - SANTIAGO DE SURCO  DISTRITO DE SANTIAGO DE SURCO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>221872.89</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="n">
+        <v>43173</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>43175</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2383312</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 7044 SAN MARTIN DE PORRES - CHORRILLOS EN LA LOCALIDAD CHORRILLOS, DISTRITO DE CHORRILLOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>112489.63</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O57" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2383315</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 7086 LOS PRECURSORES - SANTIAGO DE SURCO  DISTRITO DE SANTIAGO DE SURCO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>173169.77</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="n">
+        <v>43173</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>43178</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2383708</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 6087 PABLO MARIA GUZMAN - SANTIAGO DE SURCO  DISTRITO DE SANTIAGO DE SURCO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>247894.38</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="n">
+        <v>43182</v>
+      </c>
+      <c r="O59" s="1" t="n">
+        <v>43187</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2383712</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0171 02 - SAN JUAN DE LURIGANCHO  DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>172094.52</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="n">
+        <v>43182</v>
+      </c>
+      <c r="O60" s="1" t="n">
+        <v>43186</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2383715</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 6151 SAN LUIS GONZAGA - SAN JUAN DE MIRAFLORES  DISTRITO DE SAN JUAN DE MIRAFLORES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>205978.53</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="n">
+        <v>43173</v>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>43175</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2383719</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 6094 SANTA ROSA - CHORRILLOS EN LA LOCALIDAD CHORRILLOS, DISTRITO DE CHORRILLOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>164259.24</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O62" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2383721</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE GLORIOSOS HUSARES DE JUNIN - EL AGUSTINO EN LA LOCALIDAD EL AGUSTINO, DISTRITO DE EL AGUSTINO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>179992.8</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="n">
+        <v>43172</v>
+      </c>
+      <c r="O63" s="1" t="n">
+        <v>43175</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2383722</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0009 JOSE MARIA ARGUEDAS - EL AGUSTINO  DISTRITO DE EL AGUSTINO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>88176.07000000001</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="n">
+        <v>43153</v>
+      </c>
+      <c r="O64" s="1" t="n">
+        <v>43180</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2383726</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 6096 ANTONIO RAIMONDI - SAN JUAN DE MIRAFLORES  DISTRITO DE SAN JUAN DE MIRAFLORES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>698477.58</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O65" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2383732</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 3003 SAN CRISTOBAL - RIMAC  DISTRITO DE RIMAC, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>109817.19</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="N66" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O66" s="1" t="n">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2383735</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 2083 VIRGEN DEL CARMEN - RIMAC EN LA LOCALIDAD RIMAC, DISTRITO DE RIMAC, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>227553.42</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O67" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2383738</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE JUAN PABLO VIZCARDO Y GUZMAN - LIMA  DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>303955.93</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="O68" s="1" t="n">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2383739</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE ESTADOS UNIDOS - COMAS  DISTRITO DE COMAS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>558681.23</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="O69" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2383751</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 0059 SANTA MARIA GORETTI - LURIGANCHO  DISTRITO DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>77536.85000000001</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="n">
+        <v>43173</v>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>43175</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2383760</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 126 JAVIER PEREZ DE CUELLAR - SAN JUAN DE LURIGANCHO EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>642395.95</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="O71" s="1" t="n">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2383762</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 1128 SAN LUIS - SAN LUIS EN LA LOCALIDAD SAN LUIS, DISTRITO DE SAN LUIS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>349642.8</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="O72" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2383763</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 1236 - ATE EN LA LOCALIDAD VITARTE, DISTRITO DE ATE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>97261.24000000001</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O73" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2383765</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 7076 LAS BRISAS DE VILLA - CHORRILLOS EN LA LOCALIDAD CHORRILLOS, DISTRITO DE CHORRILLOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>52733.45</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="N74" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O74" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2383767</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 2040 REPUBLICA DE CUBA - COMAS  DISTRITO DE COMAS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>316011.06</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N75" s="1" t="n">
+        <v>43157</v>
+      </c>
+      <c r="O75" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2383770</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO; EN EL(LA) IE 1209 MARISCAL TORIBIO DE LUZURIAGA - ATE EN LA LOCALIDAD VITARTE, DISTRITO DE ATE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUCACIÓN SECUNDARIA
+</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>137727.96</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N76" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="O76" s="1" t="n">
+        <v>43168</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2410345</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE AULA; REPARACIÓN DE AMBIENTE U OFICINA PARA PRESTACION DE SERVICIOS AL PUBLICO; ADQUISICIÓN DE COMPUTADORES DE ESCRITORIO, MESAS Y AMBIENTE U OFICINA PARA PRESTACION DE SERVICIOS AL PUBLICO; EN EL(LA) IE 81772 - CHAO EN LA LOCALIDAD SAN CARLOS ALTO, DISTRITO DE CHAO, PROVINCIA VIRU, DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2875255.01</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>CHAO</t>
+        </is>
+      </c>
+      <c r="N77" s="1" t="n">
+        <v>43186</v>
+      </c>
+      <c r="O77" s="1" t="n">
+        <v>43187</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2437025</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA; CONSTRUCCIÓN DE CERCO DE LADRILLO/CONCRETO; EN EL(LA) IE 7219 ARISTOTELES - SAN JUAN DE MIRAFLORES PAMPAS DE SAN JUAN SECTOR III DISTRITO DE SAN JUAN DE MIRAFLORES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>891364.47</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="N78" s="1" t="n">
+        <v>43500</v>
+      </c>
+      <c r="O78" s="1" t="n">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2439595</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 7076 LAS BRISAS DE VILLA, EN LA LOCALIDAD CHORRILLOS, DISTRITO DE CHORRILLOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1433092.87</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O79" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2439596</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0009 JOSE MARIA ARGUEDAS EN LA LOCALIDAD EL AGUSTINO, DISTRITO DE EL AGUSTINO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>96237.11</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O80" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2439599</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 3003 SAN CRISTOBAL EN LA LOCALIDAD RIMAC, DISTRITO DE RIMAC, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>866917.8199999999</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="N81" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O81" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2439600</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0377 DIVINO NIÑO JESUS, DISTRITO DE LOS OLIVOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>283681.75</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="N82" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O82" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2439602</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 117 RVDO. PADRE PASCUAL ALEGRE GONZALES EN LA LOCALIDAD LIMA, DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>226910.67</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N83" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O83" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2439603</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 3038 PATRICIA CARMEN GUZMAN, DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>93413.28</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N84" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O84" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2439606</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 555 INMACULADA CONCEPCION, DISTRITO DE SANTIAGO DE SURCO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>674299.53</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="N85" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O85" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2439610</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 1209 MARISCAL TORIBIO DE LUZURIAGA, DISTRITO DE ATE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>152953.96</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N86" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O86" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2439613</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE LUIS ENRIQUE XIX, DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>399471.4</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N87" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O87" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2439615</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 2083 VIRGEN DEL CARMEN, DISTRITO DE RIMAC, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>1127456.09</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="N88" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O88" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2439617</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 6094 SANTA ROSA, DISTRITO DE CHORRILLOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>179485.24</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="N89" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O89" s="1" t="n">
+        <v>43532</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2439618</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 6151 SAN LUIS GONZAGA, DISTRITO DE SAN JUAN DE MIRAFLORES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>225454.52</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="N90" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O90" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2439620</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE GRAN MARISCAL ANDRES A.CACERES D. - DISTRITO DE EL AGUSTINO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>1273260.36</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="N91" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O91" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2439624</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 7086 LOS PRECURSORES, EN LA LOCALIDAD SANTIAGO DE SURCO, DISTRITO DE SANTIAGO DE SURCO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>442536.8</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="N92" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O92" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2439626</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE MI MUNDO FELIZ  EN LA LOCALIDAD SAN MARTIN DE PORRES, DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>72074</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N93" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O93" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2439629</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE CERCO PERIMÉTRICO; EN EL(LA) CETPRO FRANCISCO GARCIA CALDERON  DISTRITO DE PUEBLO LIBRE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN TÉCNICA PRODUCTIVA</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>62004.52</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>PUEBLO LIBRE</t>
+        </is>
+      </c>
+      <c r="N94" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O94" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2439631</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 126 JAVIER PEREZ DE CUELLAR EN LA LOCALIDAD SAN JUAN DE LURIGANCHO, DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>657621.96</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N95" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O95" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2439634</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 0043 JUAN PABLO II - DISTRITO DE SAN JUAN DE LURIGANCHO, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>483128.11</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="N96" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O96" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2439636</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 1128 SAN LUIS - DISTRITO DE SAN LUIS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>366556.8</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="N97" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O97" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2439637</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE 06 REPUBLICA DOMINICANA - DISTRITO DE LIMA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN BÁSICA ESPECIAL - CEBE</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>1425658.58</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N98" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O98" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2439638</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMETRICO; EN EL(LA) IE ESTADOS UNIDOS - DISTRITO DE COMAS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>1584770.01</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N99" s="1" t="n">
+        <v>43533</v>
+      </c>
+      <c r="O99" s="1" t="n">
+        <v>43533</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2447657</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA; EN EL(LA) IE 3023 PEDRO PAULET MOSTAJO - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>896906.14</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N100" s="1" t="n">
+        <v>43599</v>
+      </c>
+      <c r="O100" s="1" t="n">
+        <v>43599</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2448256</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMÉTRICO; EN EL(LA) IE 01 - COMAS EN LA LOCALIDAD COMAS, DISTRITO DE COMAS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>577088.1</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="N101" s="1" t="n">
+        <v>43605</v>
+      </c>
+      <c r="O101" s="1" t="n">
+        <v>43620</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2448352</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO PERIMÉTRICO; EN EL(LA) IE SANTA BERNARDITA - LA VICTORIA EN LA LOCALIDAD LA VICTORIA, DISTRITO DE LA VICTORIA, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN INICIAL</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>513891.73</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="N102" s="1" t="n">
+        <v>43606</v>
+      </c>
+      <c r="O102" s="1" t="n">
+        <v>43620</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2451786</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA; EN EL(LA) IE 3044 RICARDO PALMA - SAN MARTIN DE PORRES  DISTRITO DE SAN MARTIN DE PORRES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>923870.97</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="N103" s="1" t="n">
+        <v>43635</v>
+      </c>
+      <c r="O103" s="1" t="n">
+        <v>43635</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2452516</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA; EN EL(LA) IE 7221 - SAN JUAN DE MIRAFLORES EN LA LOCALIDAD CIUDAD DE DIOS, DISTRITO DE SAN JUAN DE MIRAFLORES, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>1307940.7</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="N104" s="1" t="n">
+        <v>43641</v>
+      </c>
+      <c r="O104" s="1" t="n">
+        <v>43642</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2455907</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE MOBILIARIO DE AULA; EN II.EE. INICIAL, II.EE. PRIMARIA, II.EE. SECUNDARIA A NIVEL NACIONAL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>3969000</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="N105" s="1" t="n">
+        <v>43671</v>
+      </c>
+      <c r="O105" s="1" t="n">
+        <v>43692</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2467501</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA; EN EL(LA) IE 2007 ROSA DE LAS AMERICAS - LOS OLIVOS  DISTRITO DE LOS OLIVOS, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>654667.88</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="N106" s="1" t="n">
+        <v>43766</v>
+      </c>
+      <c r="O106" s="1" t="n">
+        <v>43767</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2471126</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION DE CERCO Y/O PORTADA; EN EL(LA) CENTRO DE FORMACION TECNICA (CFT) PRODUCCION DE MATERIALES (PROMAE) - VES EN LA LOCALIDAD VILLA EL SALVADOR, DISTRITO DE VILLA EL SALVADOR, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN TÉCNICA PRODUCTIVA</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>2652549.51</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="N107" s="1" t="n">
+        <v>43797</v>
+      </c>
+      <c r="O107" s="1" t="n">
+        <v>43798</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2508732</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO ESTRUCTURAL DE AULA DE EDUCACION PRIMARIA Y AULA DE INNOVACION PEDAGOGICA; EN EL(LA) IE 0074 FERNANDO BELAUNDE TERRY - ATE  DISTRITO DE ATE, PROVINCIA LIMA, DEPARTAMENTO LIMA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EDUCACION</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>M.E.-PROGRAMA NACIONAL DE INFRAESTRUCTURA  EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>INVERSIONES IOARR</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN PRIMARIA</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>1499893.29</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N108" s="1" t="n">
+        <v>44194</v>
+      </c>
+      <c r="O108" s="1" t="n">
+        <v>44194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>